--- a/dataset/lecture_4_output/NPASS_NPT204_RDKit_activity_output_us.xlsx
+++ b/dataset/lecture_4_output/NPASS_NPT204_RDKit_activity_output_us.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,537 +429,537 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>BalabanJ</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>BertzCT</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ipc</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>HallKierAlpha</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Kappa1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kappa2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kappa3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Phi</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Chi0</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Chi1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Chi0n</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Chi1n</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Chi2n</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Chi3n</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Chi4n</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Chi0v</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Chi1v</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Chi2v</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Chi3v</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Chi4v</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MolLogP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MolMR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MolWt</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ExactMolWt</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>HeavyAtomCount</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>HeavyAtomMolWt</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>NHOHCount</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>NOCount</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>NumHAcceptors</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>NumHDonors</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>NumHeteroatoms</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>NumRotatableBonds</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>NumValenceElectrons</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>NumAmideBonds</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>NumAromaticRings</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>NumSaturatedRings</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>NumAliphaticRings</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NumAromaticCarbocycles</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>NumAromaticHeterocycles</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>NumSaturatedCarbocycles</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>NumSaturatedHeterocycles</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>NumAliphaticCarbocycles</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>NumAliphaticHeterocycles</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>RingCount</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>FractionCSP3</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>NumSpiroAtoms</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>NumBridgeheadAtoms</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>TPSA</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>LabuteASA</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA1</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA2</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA3</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA4</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA5</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA6</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA7</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA8</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA9</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA10</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA11</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA12</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA13</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>PEOE_VSA14</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA1</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA2</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA3</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA4</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA5</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA6</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA7</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA8</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA9</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>SMR_VSA10</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA1</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA2</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA3</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA4</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA5</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA6</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA7</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA8</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA9</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA10</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA11</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>SlogP_VSA12</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA1</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA2</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA3</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA4</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA5</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA6</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA7</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA8</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA9</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA10</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>EState_VSA11</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState1</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState2</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState3</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState4</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState5</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState6</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState7</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState8</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState9</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>VSA_EState10</t>
         </is>
